--- a/feedback_forms/027_online_order_experience_feedback_contact_form--feedback_forms.xlsx
+++ b/feedback_forms/027_online_order_experience_feedback_contact_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>comment_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Comment</t>
+          <t>Comment 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>contact_number_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Contact Number</t>
+          <t>Contact Number 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>product_type</t>
+          <t>product_type_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Product Type</t>
+          <t>Product Type 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>customer_service</t>
+          <t>customer_service_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Customer Service</t>
+          <t>Customer Service 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>follow_up_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Follow Up</t>
+          <t>Follow Up 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>time_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Time 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,9 +1101,9 @@
   <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>product_type_choices</t>
+          <t>product_type_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>product_type_choices</t>
+          <t>product_type_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>customer_service_choices</t>
+          <t>customer_service_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>customer_service_choices</t>
+          <t>customer_service_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>follow_up_choices</t>
+          <t>follow_up_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>follow_up_choices</t>
+          <t>follow_up_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
